--- a/output/docs/DOC_071_SCA_report.xlsx
+++ b/output/docs/DOC_071_SCA_report.xlsx
@@ -43,7 +43,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5E0DD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6EBD6"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,9 +95,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -471,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -537,14 +529,10 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>FND-0009</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>CVE-2099-0101</t>
-        </is>
-      </c>
+          <t>FND-0018</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>High</t>
@@ -552,12 +540,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>backend/requirements.txt</t>
+          <t>jinja2==2.11.2</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>sample-imagelib 1.2.0 out-of-bounds read</t>
+          <t>jinja2 2.11.2: PYSEC-2021-66 (2.11.3)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -572,46 +560,1032 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>FND-0010</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>CVE-2099-0102</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>frontend/package-lock.json</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>sample-webframework 3.0.1 uncontrolled resource consumption</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>FND-0019</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>jinja2 2.11.2: PYSEC-2026-1473 (3.1.3)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>FND-0020</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>jinja2 2.11.2: PYSEC-2026-1471 (3.1.6)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Remediate / upgrade; verified on retest.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Total findings: 2</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>FND-0021</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>jinja2 2.11.2: PYSEC-2026-1474 (3.1.4)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FND-0022</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>jinja2==2.11.2</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>jinja2 2.11.2: PYSEC-2026-1475 (3.1.5)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FND-0023</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>pyyaml==5.3</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>pyyaml 5.3: PYSEC-2020-96 (5.3.1)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>FND-0024</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>pyyaml==5.3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>pyyaml 5.3: PYSEC-2021-142 (5.4)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>FND-0025</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>pyyaml==5.3</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>pyyaml 5.3: PYSEC-2021-142 (5.4)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>FND-0026</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>pyyaml==5.3</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>pyyaml 5.3: PYSEC-2020-96 (5.3.1)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>FND-0027</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2018-28 (2.20.0)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>FND-0028</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2023-74 (2.31.0)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>FND-0029</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2023-74 (2.31.0)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>FND-0030</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2026-1873 (2.32.0)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>FND-0031</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2026-1872 (2.32.4)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>FND-0032</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>requests==2.19.0</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>requests 2.19.0: PYSEC-2026-2275 (2.33.0)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>FND-0033</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>idna==2.7</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>idna 2.7: PYSEC-2024-60 (3.7)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>FND-0034</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>idna==2.7</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>idna 2.7: PYSEC-2024-60 (3.7)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>FND-0035</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>idna==2.7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>idna 2.7: PYSEC-2026-215 (3.15)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>FND-0036</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>idna==2.7</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>idna 2.7: PYSEC-2026-215 (3.15)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>FND-0037</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2019-133 (1.24.2)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>FND-0038</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2019-132 (1.24.3)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>FND-0039</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2020-148 (1.25.9)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>FND-0040</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-192 (1.26.17,2.0.6)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>FND-0041</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-192 (1.26.17,2.0.6)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>FND-0042</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-212 (1.26.18,2.0.7)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>FND-0043</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-207 (1.24.2)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>FND-0044</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr"/>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2023-212 (1.26.18,2.0.7)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>FND-0045</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-141 (2.7.0)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>FND-0046</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-1999 (2.5.0)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FND-0047</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-1995 (1.26.19,2.2.2)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FND-0048</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-1994 (2.6.0)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FND-0049</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>urllib3==1.23</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>urllib3 1.23: PYSEC-2026-1996 (2.6.3)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Total findings: 32</t>
         </is>
       </c>
     </row>
